--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_20/return_r2/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_20/return_r2/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,16 +462,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.01985498280403597</v>
+        <v>0.05074608136501779</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2904681486126296</v>
+        <v>0.1785295280881089</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.170100130605597</v>
+        <v>0.3188191066077068</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.2390390316239549</v>
+        <v>0.4584625858468565</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.182799013211179</v>
+        <v>0.1639947103413999</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.1228990348721514</v>
+        <v>0.3508152535239864</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>47.18902206597932</v>
+        <v>23.59818693369604</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.321059870546898</v>
+        <v>0.1314631893081004</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2564409009886989</v>
+        <v>0.2987863949086496</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.501074033114723</v>
+        <v>0.5294149486542562</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.946886232813574</v>
+        <v>0.7805776178531846</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3487907250468845</v>
+        <v>0.1392399077718417</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.9513930922573468</v>
+        <v>0.9857281623960834</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>55.10928326998203</v>
+        <v>38.34691858560242</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.02690304457977333</v>
+        <v>-0.1049248124588178</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2234760871109016</v>
+        <v>0.2362625360551149</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.1683821160481263</v>
+        <v>-0.4335577483448799</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.2443803090402148</v>
+        <v>-0.5955420644902252</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2412390555896488</v>
+        <v>0.1909740557072879</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.1161925475494736</v>
+        <v>-0.5708383186326759</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>51.38242250709748</v>
+        <v>50.80659455284205</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.01173493857312247</v>
+        <v>0.2843472828880211</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2601844493393523</v>
+        <v>0.3431037584524673</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.117524606225176</v>
+        <v>0.8863922054369733</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.1851739398194411</v>
+        <v>1.35630679228745</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2198205884786031</v>
+        <v>0.1603163195649202</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.05560355024830541</v>
+        <v>1.856938483779404</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>67.56436134641943</v>
+        <v>54.02906493178627</v>
       </c>
     </row>
     <row r="6">
@@ -636,29 +636,57 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.4375224361766108</v>
+        <v>0.6493029548725378</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2671225895270363</v>
+        <v>0.2780958189586267</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.487447739074404</v>
+        <v>1.953394864551924</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.221572985253156</v>
+        <v>2.928949332418133</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1677454890097224</v>
+        <v>0.1463987043828378</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.724218543001345</v>
+        <v>4.645888853301269</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>60.2375863695462</v>
+        <v>61.74704780431389</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026年截至07-31</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.7428006166560586</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.4036465587549084</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>2.66245189648791</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>4.424384671901662</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.09941454866024901</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>17.47832378252658</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>51.20253201697178</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H6"/>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>